--- a/从零开始学Slots/从零开始学Slots-03-基础篇-玩法类型.xlsx
+++ b/从零开始学Slots/从零开始学Slots-03-基础篇-玩法类型.xlsx
@@ -9638,6 +9638,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N260" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -10303,5 +10306,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M69" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-03-基础篇-玩法类型.xlsx
+++ b/从零开始学Slots/从零开始学Slots-03-基础篇-玩法类型.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="266">
   <si>
     <r>
       <rPr>
@@ -8146,7 +8146,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8265,6 +8265,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -9739,8 +9743,8 @@
       <c r="C7" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>192</v>
+      <c r="D7" s="30">
+        <v>6</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
